--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-process-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-process-easy.xlsx
@@ -460,19 +460,19 @@
         <v>STLC bắt đầu bằng phân tích yêu cầu (Requirement Analysis) để xác định xem cái gì có thể test được (testable) và chuẩn bị các câu hỏi làm rõ nghiệp vụ.</v>
       </c>
       <c r="F2" t="str">
+        <v>Test Case Design — Thiết kế và viết chi tiết các kịch bản test case — giai đoạn thiết kế</v>
+      </c>
+      <c r="G2" t="str">
         <v>Requirement Analysis — Phân tích yêu cầu kiểm thử để xác định phạm vi và mục tiêu kiểm thử — giai đoạn phân tích</v>
       </c>
-      <c r="G2" t="str">
-        <v>Test Case Design — Thiết kế và viết chi tiết các kịch bản test case — giai đoạn thiết kế</v>
-      </c>
       <c r="H2" t="str">
+        <v>Test Closure — Tổng kết kết quả kiểm thử và ký biên bản nghiệm thu bàn giao — giai đoạn đóng test</v>
+      </c>
+      <c r="I2" t="str">
         <v>Test Execution — Tiến hành chạy thử nghiệm phần mềm và ghi nhận kết quả — giai đoạn thực thi</v>
       </c>
-      <c r="I2" t="str">
-        <v>Test Closure — Tổng kết kết quả kiểm thử và ký biên bản nghiệm thu bàn giao — giai đoạn đóng test</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Khi developer sửa xong bug, họ chuyển trạng thái bug sang Resolved (hoặc Ready for Test) để chỉ định cho QA kiểm tra lại (Retest).</v>
       </c>
       <c r="F3" t="str">
+        <v>Do Project Manager thiết lập khi họ quyết định không sửa lỗi đó trong dự án hiện tại — quản lý hoãn sửa</v>
+      </c>
+      <c r="G3" t="str">
         <v>Do Developer thiết lập khi họ đã sửa xong lỗi trong mã nguồn và sẵn sàng để QA kiểm tra lại — lập trình viên đã sửa xong</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
+        <v>Do người dùng cuối thiết lập khi họ đang chạy thử nghiệm hệ thống ở giai đoạn UAT — người dùng nghiệm thu</v>
+      </c>
+      <c r="I3" t="str">
         <v>Do QA thiết lập khi họ vừa mới phát hiện ra lỗi và nhập lên hệ thống — kiểm thử viên phát hiện</v>
       </c>
-      <c r="H3" t="str">
-        <v>Do Project Manager thiết lập khi họ quyết định không sửa lỗi đó trong dự án hiện tại — quản lý hoãn sửa</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Do người dùng cuối thiết lập khi họ đang chạy thử nghiệm hệ thống ở giai đoạn UAT — người dùng nghiệm thu</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Retesting (kiểm thử lại) tập trung chạy đúng kịch bản bị lỗi trước đó để xác nhận xem lỗi đó đã được sửa triệt để chưa. Khác với Regression testing (kiểm thử hồi quy).</v>
       </c>
       <c r="F4" t="str">
+        <v>Đo lường thời gian phản hồi của trang web khi có 100 người dùng truy cập — kiểm thử hiệu năng</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Thay đổi màu sắc của nút bấm trên giao diện theo thiết kế mới — cập nhật giao diện</v>
+      </c>
+      <c r="H4" t="str">
         <v>Xác nhận xem lỗi cụ thể đó đã thực sự được sửa thành công hay chưa — xác nhận sửa lỗi</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Tìm kiếm các lỗi mới phát sinh ở các khu vực không liên quan khác của phần mềm — kiểm thử hồi quy</v>
       </c>
-      <c r="H4" t="str">
-        <v>Đo lường thời gian phản hồi của trang web khi có 100 người dùng truy cập — kiểm thử hiệu năng</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Thay đổi màu sắc của nút bấm trên giao diện theo thiết kế mới — cập nhật giao diện</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>Liệt kê chi tiết các bước nhập liệu cụ thể cho từng màn hình của ứng dụng — kịch bản chi tiết</v>
       </c>
       <c r="H5" t="str">
+        <v>Biên bản họp bàn giao sản phẩm giữa đội phát triển và khách hàng — biên bản bàn giao</v>
+      </c>
+      <c r="I5" t="str">
         <v>Ghi chép mã nguồn của các kịch bản kiểm thử tự động viết bằng ngôn ngữ Java — mã nguồn test</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Biên bản họp bàn giao sản phẩm giữa đội phát triển và khách hàng — biên bản bàn giao</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Lỗi sập nguồn ngay khi mở app là lỗi Blocker vì nó ngăn cản hoàn toàn việc tiếp cận và test các tính năng khác của phần mềm.</v>
       </c>
       <c r="F6" t="str">
+        <v>Minor — lỗi hiển thị giao diện nhẹ không ảnh hưởng đến chức năng nghiệp vụ — lỗi giao diện nhẹ</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Trivial — lỗi viết sai chính tả trong phần tài liệu hướng dẫn sử dụng — lỗi chính tả tài liệu</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Major — lỗi lớn nhưng người dùng vẫn có cách khác để sử dụng tính năng — lỗi lớn có giải pháp thay thế</v>
+      </c>
+      <c r="I6" t="str">
         <v>Blocker / Critical — lỗi chặn đứng toàn bộ hoạt động kiểm thử các chức năng tiếp theo — lỗi chặn dòng</v>
       </c>
-      <c r="G6" t="str">
-        <v>Major — lỗi lớn nhưng người dùng vẫn có cách khác để sử dụng tính năng — lỗi lớn có giải pháp thay thế</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Minor — lỗi hiển thị giao diện nhẹ không ảnh hưởng đến chức năng nghiệp vụ — lỗi giao diện nhẹ</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Trivial — lỗi viết sai chính tả trong phần tài liệu hướng dẫn sử dụng — lỗi chính tả tài liệu</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Priority (Độ ưu tiên) thể hiện độ khẩn cấp cần sửa (do PO hoặc PM quyết định). Severity (Mức độ nghiêm trọng) thể hiện mức độ phá hủy chức năng phần mềm (do QA quyết định).</v>
       </c>
       <c r="F7" t="str">
-        <v>Mức độ khẩn cấp cần phải sửa lỗi đó trước hay sau từ góc nhìn kinh doanh/tiến độ dự án — mức độ khẩn cấp sửa lỗi</v>
+        <v>Số lượng dòng code mà lập trình viên cần viết để sửa xong lỗi đó — độ dài sửa code</v>
       </c>
       <c r="G7" t="str">
         <v>Mức độ tác động kỹ thuật của lỗi đó đối với kiến trúc hệ thống bên trong — tác động kỹ thuật</v>
       </c>
       <c r="H7" t="str">
-        <v>Số lượng dòng code mà lập trình viên cần viết để sửa xong lỗi đó — độ dài sửa code</v>
+        <v>Mức lương hàng tháng của lập trình viên chịu trách nhiệm sửa lỗi đó — chi phí sửa lỗi</v>
       </c>
       <c r="I7" t="str">
-        <v>Mức lương hàng tháng của lập trình viên chịu trách nhiệm sửa lỗi đó — chi phí sửa lỗi</v>
+        <v>Mức độ khẩn cấp cần phải sửa lỗi đó trước hay sau từ góc nhìn kinh doanh/tiến độ dự án — mức độ khẩn cấp sửa lỗi</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -658,10 +658,10 @@
         <v>Developer từ chối sửa lỗi vì cho rằng đó là tính năng thiết kế đúng — developer từ chối sửa</v>
       </c>
       <c r="H8" t="str">
+        <v>Khách hàng đồng ý nghiệm thu tính năng bất chấp lỗi vẫn đang tồn tại — nghiệm thu chấp nhận lỗi</v>
+      </c>
+      <c r="I8" t="str">
         <v>Project Manager quyết định hoãn việc sửa lỗi này sang dự án năm sau — hoãn sửa lỗi</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Khách hàng đồng ý nghiệm thu tính năng bất chấp lỗi vẫn đang tồn tại — nghiệm thu chấp nhận lỗi</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,10 +684,10 @@
         <v>Test Case Specification chứa các test cases chi tiết gồm: ID, Title, Pre-condition, Steps, Test Data, Expected Result, Actual Result, Status.</v>
       </c>
       <c r="F9" t="str">
+        <v>Mã nguồn Java/Python dùng để cấu hình tự động chạy CI/CD cho dự án — cấu hình CI/CD</v>
+      </c>
+      <c r="G9" t="str">
         <v>Danh sách các kịch bản kiểm thử chi tiết bao gồm điều kiện tiên quyết, các bước thực hiện, dữ liệu test và kết quả mong đợi — đặc tả kịch bản test</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Mã nguồn Java/Python dùng để cấu hình tự động chạy CI/CD cho dự án — cấu hình CI/CD</v>
       </c>
       <c r="H9" t="str">
         <v>Bản vẽ thiết kế giao diện đồ họa chi tiết của trang web bán hàng — bản vẽ thiết kế</v>
@@ -696,7 +696,7 @@
         <v>Báo cáo doanh số bán hàng hàng tháng của doanh nghiệp khách hàng — báo cáo doanh số</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Lập báo cáo tổng kết kiểm thử (Test Summary Report), đánh giá các chỉ số lỗi và lưu trữ các test assets — đóng quy trình kiểm thử</v>
       </c>
       <c r="G10" t="str">
+        <v>Gửi email yêu cầu khách hàng thanh toán nốt 50% chi phí hợp đồng còn lại — thanh toán chi phí</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Tổ chức tiệc liên hoan chúc mừng sinh nhật cho các thành viên trong công ty — liên hoan nội bộ</v>
+      </c>
+      <c r="I10" t="str">
         <v>Bắt đầu ngồi viết mã nguồn code các tính năng Backend bằng ngôn ngữ Java — lập trình tính năng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Gửi email yêu cầu khách hàng thanh toán nốt 50% chi phí hợp đồng còn lại — thanh toán chi phí</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Tổ chức tiệc liên hoan chúc mừng sinh nhật cho các thành viên trong công ty — liên hoan nội bộ</v>
       </c>
       <c r="J10">
         <v>1</v>
